--- a/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_VGA.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/shot_packs/shot_pack_VGA.xlsx
@@ -666,7 +666,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
